--- a/artfynd/A 52601-2025 artfynd.xlsx
+++ b/artfynd/A 52601-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127273029</v>
       </c>
       <c r="B2" t="n">
-        <v>98489</v>
+        <v>98457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127273030</v>
+        <v>127273022</v>
       </c>
       <c r="B3" t="n">
-        <v>98489</v>
+        <v>98340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,28 +801,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562383</v>
+        <v>562351</v>
       </c>
       <c r="R3" t="n">
-        <v>6917270</v>
+        <v>6917299</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127273022</v>
+        <v>127273030</v>
       </c>
       <c r="B4" t="n">
-        <v>98372</v>
+        <v>98457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,28 +916,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562351</v>
+        <v>562383</v>
       </c>
       <c r="R4" t="n">
-        <v>6917299</v>
+        <v>6917270</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
         <v>127273018</v>
       </c>
       <c r="B5" t="n">
-        <v>95319</v>
+        <v>95288</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>127273034</v>
       </c>
       <c r="B6" t="n">
-        <v>98491</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>127273021</v>
       </c>
       <c r="B7" t="n">
-        <v>98372</v>
+        <v>98340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>127273023</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52601-2025 artfynd.xlsx
+++ b/artfynd/A 52601-2025 artfynd.xlsx
@@ -1483,7 +1483,7 @@
         <v>131143934</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>131143933</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131143935</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 52601-2025 artfynd.xlsx
+++ b/artfynd/A 52601-2025 artfynd.xlsx
@@ -1483,7 +1483,7 @@
         <v>131143934</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>131143933</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131143935</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 52601-2025 artfynd.xlsx
+++ b/artfynd/A 52601-2025 artfynd.xlsx
@@ -1483,7 +1483,7 @@
         <v>131143934</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>131143933</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131143935</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 52601-2025 artfynd.xlsx
+++ b/artfynd/A 52601-2025 artfynd.xlsx
@@ -1483,7 +1483,7 @@
         <v>131143934</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>131143933</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131143935</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 52601-2025 artfynd.xlsx
+++ b/artfynd/A 52601-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273018</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143931</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143933</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143934</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143935</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143919</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143916</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273034</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273021</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1748,6 +1798,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273022</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273023</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1978,6 +2038,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273029</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,8 +2158,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273030</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>